--- a/SalesManager/Templates/WeeklyReportTemplate.xlsx
+++ b/SalesManager/Templates/WeeklyReportTemplate.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\n-azuma\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\n-azuma\Documents\azuma\学習\アプリ開発\アプリ③\SalesManager\SalesManager\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CAC2E8-7AA0-4178-BA8E-2C5687A731E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F2096C-E9E0-4E96-8C7D-0F69890CC5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60960" yWindow="3375" windowWidth="17700" windowHeight="12195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="シート1" sheetId="1" r:id="rId1"/>
+    <sheet name="週次報告書" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,8 +63,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    <numFmt numFmtId="177" formatCode="&quot;¥&quot;#,##0_);[Red]\(&quot;¥&quot;#,##0\)"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -89,12 +90,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="&quot;ＭＳ Ｐゴシック&quot;"/>
@@ -114,6 +109,13 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="4">
@@ -136,7 +138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -174,27 +176,99 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="8">
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;¥&quot;#,##0_);[Red]\(&quot;¥&quot;#,##0\)"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
+      <border>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -222,9 +296,9 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="シート1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="firstRowStripe" dxfId="6"/>
+      <tableStyleElement type="secondRowStripe" dxfId="5"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -243,11 +317,11 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="商品ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="商品名"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="先週販売数（集計）"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="現在在庫数"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="販売後在庫"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="発注対象（5以下）"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="累計売上金額"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="先週販売数（集計）" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="現在在庫数" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="販売後在庫" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="発注対象（5以下）" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="累計売上金額" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="シート1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -491,34 +565,34 @@
     <row r="2" spans="1:7" ht="17.399999999999999">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="5"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="8"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" thickBot="1">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="1:7" ht="26.25" customHeight="1">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7" t="s">
+    <row r="4" spans="1:7" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6"/>
+  <phoneticPr fontId="5"/>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
